--- a/NEW BOT 02/Finished_Goods_FAN_Floor_Stock_Movement.xlsx
+++ b/NEW BOT 02/Finished_Goods_FAN_Floor_Stock_Movement.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Warehouse Module ⟶ Warehouse Reports ⟶ Stock Movement Report(222) ⟶ Item Sub Group: Finished Goods ⟶ Warehouse: FAN Floor  |  Date Range: 2026-09-01 to 2026-09-19</t>
+          <t>Warehouse Module ⟶ Warehouse Reports ⟶ Stock Movement Report(222) ⟶ Item Sub Group: Finished Goods ⟶ Warehouse: FAN Floor  |  Date Range: 2026-09-01 to 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>5,417.00</t>
+          <t>14,539.00</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -2100,10 +2100,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="K24" s="16" t="n">
         <v>0</v>
@@ -2112,16 +2112,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="N24" s="16" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>2145.88656143</v>
+        <v>2146.96703217</v>
       </c>
       <c r="Q24" s="15" t="inlineStr"/>
     </row>
@@ -2771,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="K35" s="19" t="n">
         <v>0</v>
@@ -2783,16 +2783,16 @@
         <v>0</v>
       </c>
       <c r="M35" s="19" t="n">
-        <v>8580</v>
+        <v>9330</v>
       </c>
       <c r="N35" s="19" t="n">
-        <v>8580</v>
+        <v>9330</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P35" s="19" t="n">
-        <v>2469.23633097</v>
+        <v>2470.81570254</v>
       </c>
       <c r="Q35" s="18" t="inlineStr"/>
     </row>
@@ -3808,10 +3808,10 @@
         <v>0</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="K52" s="16" t="n">
         <v>0</v>
@@ -3820,16 +3820,16 @@
         <v>0</v>
       </c>
       <c r="M52" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="N52" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>1768.7493255</v>
+        <v>1769.02339024</v>
       </c>
       <c r="Q52" s="15" t="inlineStr"/>
     </row>
@@ -5150,10 +5150,10 @@
         <v>0</v>
       </c>
       <c r="I74" s="16" t="n">
-        <v>90800</v>
+        <v>99872</v>
       </c>
       <c r="J74" s="16" t="n">
-        <v>92480</v>
+        <v>101552</v>
       </c>
       <c r="K74" s="16" t="n">
         <v>0</v>
@@ -5168,10 +5168,10 @@
         <v>92448</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>32</v>
+        <v>9104</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>45.44311879</v>
+        <v>45.46119718</v>
       </c>
       <c r="Q74" s="15" t="inlineStr"/>
     </row>
@@ -13675,16 +13675,16 @@
       <c r="H214" s="20" t="n"/>
       <c r="I214" s="20" t="n"/>
       <c r="J214" s="21" t="n">
-        <v>218677</v>
+        <v>228740</v>
       </c>
       <c r="K214" s="20" t="n"/>
       <c r="L214" s="20" t="n"/>
       <c r="M214" s="20" t="n"/>
       <c r="N214" s="21" t="n">
-        <v>213260</v>
+        <v>214201</v>
       </c>
       <c r="O214" s="21" t="n">
-        <v>5417</v>
+        <v>14539</v>
       </c>
       <c r="P214" s="20" t="n"/>
       <c r="Q214" s="20" t="n"/>
